--- a/diseases/d020/2010-2014.xlsx
+++ b/diseases/d020/2010-2014.xlsx
@@ -1209,9 +1209,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1801,9 +1798,6 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -2393,9 +2387,6 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
@@ -2985,9 +2976,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -3577,9 +3565,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -4317,9 +4302,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -5057,9 +5039,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -5797,9 +5776,6 @@
       <c r="O36" t="n">
         <v>2</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.0041009378178387</v>
       </c>
@@ -6537,9 +6513,6 @@
       <c r="O41" t="n">
         <v>11</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.02255515799811285</v>
       </c>
@@ -7277,9 +7250,6 @@
       <c r="O46" t="n">
         <v>7</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.01435328236243545</v>
       </c>
@@ -7869,9 +7839,6 @@
       <c r="O50" t="n">
         <v>6</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.0123028134535161</v>
       </c>
@@ -8609,9 +8576,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -9201,9 +9165,6 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
@@ -9793,9 +9754,6 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -10385,9 +10343,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -10977,9 +10932,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -11569,9 +11521,6 @@
       <c r="O75" t="n">
         <v>1</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0.002035513875197372</v>
       </c>
@@ -12161,9 +12110,6 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
@@ -12901,9 +12847,6 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
@@ -13641,9 +13584,6 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -14381,9 +14321,6 @@
       <c r="O94" t="n">
         <v>1</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.002035513875197372</v>
       </c>
@@ -15121,9 +15058,6 @@
       <c r="O99" t="n">
         <v>1</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.002035513875197372</v>
       </c>
@@ -15713,9 +15647,6 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -16305,9 +16236,6 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
@@ -16897,9 +16825,6 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -17489,9 +17414,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -18081,9 +18003,6 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -18673,9 +18592,6 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0</v>
       </c>
@@ -19265,9 +19181,6 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0</v>
       </c>
@@ -20005,9 +19918,6 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
@@ -20745,9 +20655,6 @@
       <c r="O137" t="n">
         <v>0</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0</v>
       </c>
@@ -21485,9 +21392,6 @@
       <c r="O142" t="n">
         <v>1</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0.002016146124787207</v>
       </c>
@@ -22077,9 +21981,6 @@
       <c r="O146" t="n">
         <v>7</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0.01411302287351045</v>
       </c>
@@ -23261,9 +23162,6 @@
       <c r="O154" t="n">
         <v>10</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0.02016146124787207</v>
       </c>
@@ -24593,9 +24491,6 @@
       <c r="O163" t="n">
         <v>1</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0.002016146124787207</v>
       </c>
@@ -26073,9 +25968,6 @@
       <c r="O173" t="n">
         <v>1</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0.002016146124787207</v>
       </c>
@@ -27257,9 +27149,6 @@
       <c r="O181" t="n">
         <v>0</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="R181" t="n">
         <v>0</v>
       </c>
@@ -28589,9 +28478,6 @@
       <c r="O190" t="n">
         <v>0</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0</v>
       </c>
@@ -29773,9 +29659,6 @@
       <c r="O198" t="n">
         <v>0</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0</v>
       </c>
@@ -30957,9 +30840,6 @@
       <c r="O206" t="n">
         <v>0</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0</v>
       </c>
@@ -32141,9 +32021,6 @@
       <c r="O214" t="n">
         <v>0</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>0</v>
       </c>
@@ -33621,9 +33498,6 @@
       <c r="O224" t="n">
         <v>0</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0</v>
       </c>
@@ -34953,9 +34827,6 @@
       <c r="O233" t="n">
         <v>0</v>
       </c>
-      <c r="Q233" t="n">
-        <v>0</v>
-      </c>
       <c r="R233" t="n">
         <v>0</v>
       </c>
@@ -36285,9 +36156,6 @@
       <c r="O242" t="n">
         <v>1</v>
       </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
       <c r="R242" t="n">
         <v>0.001997157465750572</v>
       </c>
@@ -37617,9 +37485,6 @@
       <c r="O251" t="n">
         <v>7</v>
       </c>
-      <c r="Q251" t="n">
-        <v>0</v>
-      </c>
       <c r="R251" t="n">
         <v>0.013980102260254</v>
       </c>
@@ -38801,9 +38666,6 @@
       <c r="O259" t="n">
         <v>3</v>
       </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
       <c r="R259" t="n">
         <v>0.005991472397251715</v>
       </c>
@@ -40133,9 +39995,6 @@
       <c r="O268" t="n">
         <v>3</v>
       </c>
-      <c r="Q268" t="n">
-        <v>0</v>
-      </c>
       <c r="R268" t="n">
         <v>0.005991472397251715</v>
       </c>
@@ -41317,9 +41176,6 @@
       <c r="O276" t="n">
         <v>0</v>
       </c>
-      <c r="Q276" t="n">
-        <v>0</v>
-      </c>
       <c r="R276" t="n">
         <v>0</v>
       </c>
@@ -42501,9 +42357,6 @@
       <c r="O284" t="n">
         <v>0</v>
       </c>
-      <c r="Q284" t="n">
-        <v>0</v>
-      </c>
       <c r="R284" t="n">
         <v>0</v>
       </c>
@@ -43833,9 +43686,6 @@
       <c r="O293" t="n">
         <v>0</v>
       </c>
-      <c r="Q293" t="n">
-        <v>0</v>
-      </c>
       <c r="R293" t="n">
         <v>0</v>
       </c>
@@ -45017,9 +44867,6 @@
       <c r="O301" t="n">
         <v>0</v>
       </c>
-      <c r="Q301" t="n">
-        <v>0</v>
-      </c>
       <c r="R301" t="n">
         <v>0</v>
       </c>
@@ -46201,9 +46048,6 @@
       <c r="O309" t="n">
         <v>0</v>
       </c>
-      <c r="Q309" t="n">
-        <v>0</v>
-      </c>
       <c r="R309" t="n">
         <v>0</v>
       </c>
@@ -47385,9 +47229,6 @@
       <c r="O317" t="n">
         <v>0</v>
       </c>
-      <c r="Q317" t="n">
-        <v>0</v>
-      </c>
       <c r="R317" t="n">
         <v>0</v>
       </c>
@@ -48717,9 +48558,6 @@
       <c r="O326" t="n">
         <v>1</v>
       </c>
-      <c r="Q326" t="n">
-        <v>0</v>
-      </c>
       <c r="R326" t="n">
         <v>0.001978667765170246</v>
       </c>
@@ -50049,9 +49887,6 @@
       <c r="O335" t="n">
         <v>0</v>
       </c>
-      <c r="Q335" t="n">
-        <v>0</v>
-      </c>
       <c r="R335" t="n">
         <v>0</v>
       </c>
@@ -51529,9 +51364,6 @@
       <c r="O345" t="n">
         <v>0</v>
       </c>
-      <c r="Q345" t="n">
-        <v>0</v>
-      </c>
       <c r="R345" t="n">
         <v>0</v>
       </c>
@@ -52861,9 +52693,6 @@
       <c r="O354" t="n">
         <v>9</v>
       </c>
-      <c r="Q354" t="n">
-        <v>0</v>
-      </c>
       <c r="R354" t="n">
         <v>0.01780800988653221</v>
       </c>
@@ -54045,9 +53874,6 @@
       <c r="O362" t="n">
         <v>13</v>
       </c>
-      <c r="Q362" t="n">
-        <v>0</v>
-      </c>
       <c r="R362" t="n">
         <v>0.02572268094721319</v>
       </c>
@@ -55525,9 +55351,6 @@
       <c r="O372" t="n">
         <v>3</v>
       </c>
-      <c r="Q372" t="n">
-        <v>0</v>
-      </c>
       <c r="R372" t="n">
         <v>0.005936003295510736</v>
       </c>
@@ -56707,9 +56530,6 @@
         <v>0</v>
       </c>
       <c r="O380" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q380" t="n">
         <v>0</v>
       </c>
       <c r="R380" t="n">
